--- a/data/شیراز.xlsx
+++ b/data/شیراز.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v.pishdad\Downloads\برنامه ها فروشگاه ها\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v.pishdad\Downloads\برنامه ها فروشگاه ها\ادیت\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D95C6FE-D5FE-45BB-8FC6-5F0037A37943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11280550-D39A-4E34-866C-11BEDC6FA280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="91">
   <si>
     <t>نام فروشگاه</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>استند پوزیترون سفارش گذاری</t>
+  </si>
+  <si>
+    <t>مرداد</t>
+  </si>
+  <si>
+    <t>شیراز</t>
   </si>
 </sst>
 </file>
@@ -588,29 +594,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF25F5C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF173A12"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF96D95E"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <b/>
@@ -877,7 +861,7 @@
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1">
       <c r="A1" s="12" t="str">
         <f>IF(B2="","فرم ارزیابی دوره‌ای فروشگاه","ارزیابی فروشگاه "&amp;B2&amp;" — "&amp;D2&amp;" "&amp;F2)</f>
-        <v>فرم ارزیابی دوره‌ای فروشگاه</v>
+        <v>ارزیابی فروشگاه شیراز — مرداد 1405</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -889,15 +873,21 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2">
+        <v>1405</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -1889,15 +1879,15 @@
     <mergeCell ref="A66:F67"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D60">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="D2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D2" xr:uid="{FB10975F-7724-4688-84B6-ED8C81B42DFC}">
       <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D6:D60" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -1927,7 +1917,7 @@
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1">
       <c r="A1" s="12" t="str">
         <f>IF(B2="","فرم ارزیابی دوره‌ای فروشگاه","ارزیابی فروشگاه "&amp;B2&amp;" — "&amp;D2&amp;" "&amp;F2)</f>
-        <v>فرم ارزیابی دوره‌ای فروشگاه</v>
+        <v>ارزیابی فروشگاه شیراز — مرداد 1405</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1939,15 +1929,21 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2">
+        <v>1405</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
